--- a/table_from_link/37002253_table5.xlsx
+++ b/table_from_link/37002253_table5.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rsID (CHR:BP:Effect Allele)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Microbiome Genera</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t># cohorts</t>
         </is>
@@ -471,33 +483,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>− 0.044</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
+          <t>− 0.044</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.015</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>− 2.881</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0040</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>18173</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>− 2.881</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18173</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -513,33 +517,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>− 0.044</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
+          <t>− 0.044</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>− 2.241</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.0250</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10657</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>− 2.241</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10657</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -558,30 +554,22 @@
           <t>0.030</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
+      <c r="D4" t="n">
+        <v>0.015</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>2.127</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.0334</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>17494</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17494</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -600,30 +588,22 @@
           <t>0.033</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0.015</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>2.120</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.0340</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>17261</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17261</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -639,33 +619,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>− 0.035</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
+          <t>− 0.035</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.015</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>− 2.188</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.0287</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>17960</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>− 2.188</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17960</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -684,30 +656,22 @@
           <t>0.064</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.033</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0.033</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>1.993</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.0462</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3721</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -726,30 +690,22 @@
           <t>0.040</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.019</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0.019</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>2.216</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.0267</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>11291</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11291</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -768,30 +724,22 @@
           <t>0.050</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
+      <c r="D9" t="n">
+        <v>0.024</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>2.207</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.0273</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6888</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6888</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -810,30 +758,22 @@
           <t>0.044</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0.021</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>2.032</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.0421</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>9194</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9194</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -852,30 +792,22 @@
           <t>0.048</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
+      <c r="D11" t="n">
+        <v>0.021</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>2.468</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.0136</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>15637</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15637</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -894,30 +826,22 @@
           <t>0.052</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
+      <c r="D12" t="n">
+        <v>0.023</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>2.214</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.0268</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>12811</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12811</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -936,30 +860,22 @@
           <t>0.050</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.022</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0.022</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>2.344</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.0191</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>14323</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14323</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -978,30 +894,22 @@
           <t>0.053</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
+      <c r="D14" t="n">
+        <v>0.021</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>2.453</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.0142</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>14846</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14846</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1017,33 +925,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>− 0.071</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
+          <t>− 0.071</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.027</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>− 2.534</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.0113</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>9357</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>− 2.534</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9357</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1059,33 +959,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>− 0.103</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.043</t>
-        </is>
+          <t>− 0.103</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.043</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>− 2.346</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.0190</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>− 2.346</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3721</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1104,30 +996,22 @@
           <t>0.080</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
+      <c r="D17" t="n">
+        <v>0.028</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>2.901</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.0037</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>9049</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9049</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1146,30 +1030,22 @@
           <t>0.082</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
+      <c r="D18" t="n">
+        <v>0.032</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.584</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.0098</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6508</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6508</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/table_from_link/37002253_table5.xlsx
+++ b/table_from_link/37002253_table5.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rsID (CHR:BP:Effect Allele)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Microbiome Genera</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t># cohorts</t>
         </is>
@@ -483,25 +471,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>− 0.044</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.015</v>
+          <t>− 0.044</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>− 2.881</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18173</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23</v>
+          <t>− 2.881</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>18173</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -517,25 +513,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>− 0.044</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.02</v>
+          <t>− 0.044</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>− 2.241</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10657</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23</v>
+          <t>− 2.241</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0250</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10657</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -554,22 +558,30 @@
           <t>0.030</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.015</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>2.127</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17494</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0334</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>17494</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -588,22 +600,30 @@
           <t>0.033</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.015</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>2.120</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17261</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0340</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -619,25 +639,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>− 0.035</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.015</v>
+          <t>− 0.035</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>− 2.188</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17960</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23</v>
+          <t>− 2.188</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0287</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>17960</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -656,22 +684,30 @@
           <t>0.064</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0.033</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.033</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>1.993</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0.0462</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3721</v>
-      </c>
-      <c r="H7" t="n">
-        <v>13</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0462</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -690,22 +726,30 @@
           <t>0.040</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.019</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>2.216</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11291</v>
-      </c>
-      <c r="H8" t="n">
-        <v>23</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.0267</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11291</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -724,22 +768,30 @@
           <t>0.050</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.024</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>2.207</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6888</v>
-      </c>
-      <c r="H9" t="n">
-        <v>21</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0273</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -758,22 +810,30 @@
           <t>0.044</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.021</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>2.032</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0.0421</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9194</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0421</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>9194</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -792,22 +852,30 @@
           <t>0.048</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0.021</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>2.468</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="G11" t="n">
-        <v>15637</v>
-      </c>
-      <c r="H11" t="n">
-        <v>20</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0136</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>15637</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -826,22 +894,30 @@
           <t>0.052</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.023</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>2.214</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0.0268</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12811</v>
-      </c>
-      <c r="H12" t="n">
-        <v>19</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0268</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>12811</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -860,22 +936,30 @@
           <t>0.050</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0.022</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>2.344</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0.0191</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14323</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0191</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>14323</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -894,22 +978,30 @@
           <t>0.053</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.021</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>2.453</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14846</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.0142</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>14846</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -925,25 +1017,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>− 0.071</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.027</v>
+          <t>− 0.071</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>− 2.534</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.0113</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9357</v>
-      </c>
-      <c r="H15" t="n">
-        <v>20</v>
+          <t>− 2.534</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0113</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>9357</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -959,25 +1059,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>− 0.103</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.043</v>
+          <t>− 0.103</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>− 2.346</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3721</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
+          <t>− 2.346</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0190</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -996,22 +1104,30 @@
           <t>0.080</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0.028</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>2.901</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9049</v>
-      </c>
-      <c r="H17" t="n">
-        <v>20</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9049</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1030,22 +1146,30 @@
           <t>0.082</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0.032</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.584</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6508</v>
-      </c>
-      <c r="H18" t="n">
-        <v>18</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.0098</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
     </row>
   </sheetData>
